--- a/inventario_agonia.xlsx
+++ b/inventario_agonia.xlsx
@@ -1,24 +1,32 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <workbookPr codeName="ThisWorkbook"/>
+  <workbookPr/>
+  <workbookProtection/>
+  <bookViews>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+  </bookViews>
   <sheets>
-    <sheet name="Inventario" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
-      <sz val="12"/>
+      <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -29,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -37,17 +45,26 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="00000000"/>
@@ -117,81 +134,6 @@
     </indexedColors>
   </colors>
 </styleSheet>
-</file>
-
-<file path=xl/comments/comment1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <authors>
-    <author>agonia</author>
-  </authors>
-  <commentList>
-    <comment ref="F9" authorId="0" shapeId="0">
-      <text>
-        <t>stock negativo — revisar</t>
-      </text>
-    </comment>
-    <comment ref="F28" authorId="0" shapeId="0">
-      <text>
-        <t>stock negativo — revisar</t>
-      </text>
-    </comment>
-    <comment ref="F29" authorId="0" shapeId="0">
-      <text>
-        <t>stock negativo — revisar</t>
-      </text>
-    </comment>
-    <comment ref="F30" authorId="0" shapeId="0">
-      <text>
-        <t>stock negativo — revisar</t>
-      </text>
-    </comment>
-    <comment ref="F31" authorId="0" shapeId="0">
-      <text>
-        <t>stock negativo — revisar</t>
-      </text>
-    </comment>
-    <comment ref="F39" authorId="0" shapeId="0">
-      <text>
-        <t>stock negativo — revisar</t>
-      </text>
-    </comment>
-    <comment ref="F48" authorId="0" shapeId="0">
-      <text>
-        <t>stock negativo — revisar</t>
-      </text>
-    </comment>
-    <comment ref="F66" authorId="0" shapeId="0">
-      <text>
-        <t>stock negativo — revisar</t>
-      </text>
-    </comment>
-    <comment ref="F73" authorId="0" shapeId="0">
-      <text>
-        <t>stock negativo — revisar</t>
-      </text>
-    </comment>
-    <comment ref="F85" authorId="0" shapeId="0">
-      <text>
-        <t>stock negativo — revisar</t>
-      </text>
-    </comment>
-    <comment ref="F118" authorId="0" shapeId="0">
-      <text>
-        <t>stock negativo — revisar</t>
-      </text>
-    </comment>
-    <comment ref="F119" authorId="0" shapeId="0">
-      <text>
-        <t>stock negativo — revisar</t>
-      </text>
-    </comment>
-    <comment ref="F134" authorId="0" shapeId="0">
-      <text>
-        <t>stock negativo — revisar</t>
-      </text>
-    </comment>
-  </commentList>
-</comments>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -269,7 +211,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -304,7 +245,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -339,16 +279,20 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="100000"/>
-                <a:shade val="100000"/>
+                <a:shade val="51000"/>
+                <a:satMod val="130000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="80000">
+              <a:schemeClr val="phClr">
+                <a:shade val="93000"/>
                 <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:tint val="50000"/>
-                <a:shade val="100000"/>
-                <a:satMod val="350000"/>
+                <a:shade val="94000"/>
+                <a:satMod val="135000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
@@ -470,88 +414,54 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults>
-    <a:spDef>
-      <a:spPr/>
-      <a:bodyPr/>
-      <a:lstStyle/>
-      <a:style>
-        <a:lnRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="3">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </a:style>
-    </a:spDef>
-    <a:lnDef>
-      <a:spPr/>
-      <a:bodyPr/>
-      <a:lstStyle/>
-      <a:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </a:style>
-    </a:lnDef>
-  </a:objectDefaults>
+  <a:objectDefaults/>
   <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F161"/>
+  <dimension ref="A1:G161"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Tipo</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Color</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Diseño</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Talla</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Unidades</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Vendidas</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Stock</t>
         </is>
       </c>
     </row>
@@ -566,25 +476,22 @@
           <t>Blanco</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="C2" t="n">
+        <v>1</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
           <t>XC</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="E2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -598,22 +505,21 @@
           <t>Blanco</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="C3" t="n">
+        <v>1</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="E3" t="n">
+        <v>2</v>
       </c>
       <c r="F3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" t="n">
         <v>2</v>
       </c>
     </row>
@@ -628,23 +534,22 @@
           <t>Blanco</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="C4" t="n">
+        <v>1</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="E4" t="n">
+        <v>2</v>
       </c>
       <c r="F4" t="n">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -658,22 +563,21 @@
           <t>Blanco</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="C5" t="n">
+        <v>1</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
           <t>G</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="E5" t="n">
+        <v>1</v>
       </c>
       <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" t="n">
         <v>1</v>
       </c>
     </row>
@@ -688,25 +592,22 @@
           <t>Blanco</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="C6" t="n">
+        <v>1</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
           <t>XL</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -720,25 +621,22 @@
           <t>Rosa</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="C7" t="n">
+        <v>1</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
           <t>XC</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="E7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -752,23 +650,22 @@
           <t>Rosa</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="C8" t="n">
+        <v>1</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="E8" t="n">
+        <v>1</v>
       </c>
       <c r="F8" t="n">
         <v>1</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -782,23 +679,22 @@
           <t>Rosa</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="C9" t="n">
+        <v>1</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="E9" t="n">
+        <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>2</v>
+        <v>0</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -812,25 +708,22 @@
           <t>Rosa</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="C10" t="n">
+        <v>1</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
           <t>G</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="E10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -844,25 +737,22 @@
           <t>Rosa</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="C11" t="n">
+        <v>1</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
           <t>XL</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="E11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -876,25 +766,22 @@
           <t>Negro</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="C12" t="n">
+        <v>1</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
           <t>XC</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="E12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -908,25 +795,22 @@
           <t>Negro</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="C13" t="n">
+        <v>1</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="E13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -940,23 +824,22 @@
           <t>Negro</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="C14" t="n">
+        <v>1</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
+      <c r="E14" t="n">
+        <v>7</v>
       </c>
       <c r="F14" t="n">
-        <v>4</v>
+        <v>6</v>
+      </c>
+      <c r="G14" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="15">
@@ -970,24 +853,23 @@
           <t>Negro</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="C15" t="n">
+        <v>1</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
           <t>G</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="E15" t="n">
+        <v>6</v>
       </c>
       <c r="F15" t="n">
         <v>3</v>
       </c>
+      <c r="G15" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1000,25 +882,22 @@
           <t>Negro</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="C16" t="n">
+        <v>1</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
           <t>XL</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="E16" t="n">
+        <v>1</v>
+      </c>
+      <c r="F16" t="n">
+        <v>1</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -1032,25 +911,22 @@
           <t>Navy</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="C17" t="n">
+        <v>1</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
           <t>XC</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="E17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -1064,25 +940,22 @@
           <t>Navy</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="C18" t="n">
+        <v>1</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="E18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1096,25 +969,22 @@
           <t>Navy</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="C19" t="n">
+        <v>1</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="E19" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1128,25 +998,22 @@
           <t>Navy</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="C20" t="n">
+        <v>1</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
           <t>G</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="E20" t="n">
+        <v>1</v>
+      </c>
+      <c r="F20" t="n">
+        <v>1</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1160,25 +1027,22 @@
           <t>Navy</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="C21" t="n">
+        <v>1</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
           <t>XL</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="E21" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -1192,25 +1056,22 @@
           <t>Carbon</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="C22" t="n">
+        <v>1</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
           <t>XC</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="E22" t="n">
+        <v>1</v>
+      </c>
+      <c r="F22" t="n">
+        <v>1</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -1224,25 +1085,22 @@
           <t>Carbon</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="C23" t="n">
+        <v>1</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="E23" t="n">
+        <v>4</v>
+      </c>
+      <c r="F23" t="n">
+        <v>2</v>
+      </c>
+      <c r="G23" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="24">
@@ -1256,25 +1114,22 @@
           <t>Carbon</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="C24" t="n">
+        <v>1</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="E24" t="n">
+        <v>3</v>
+      </c>
+      <c r="F24" t="n">
+        <v>0</v>
+      </c>
+      <c r="G24" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="25">
@@ -1288,25 +1143,22 @@
           <t>Carbon</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="C25" t="n">
+        <v>1</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
           <t>G</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="E25" t="n">
+        <v>3</v>
+      </c>
+      <c r="F25" t="n">
+        <v>2</v>
+      </c>
+      <c r="G25" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="26">
@@ -1320,25 +1172,22 @@
           <t>Carbon</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="C26" t="n">
+        <v>1</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
           <t>XL</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="E26" t="n">
+        <v>0</v>
+      </c>
+      <c r="F26" t="n">
+        <v>0</v>
+      </c>
+      <c r="G26" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -1352,25 +1201,22 @@
           <t>Morado</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="C27" t="n">
+        <v>1</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
           <t>XC</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="E27" t="n">
+        <v>0</v>
+      </c>
+      <c r="F27" t="n">
+        <v>0</v>
+      </c>
+      <c r="G27" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -1384,23 +1230,22 @@
           <t>Morado</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="C28" t="n">
+        <v>1</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="E28" t="n">
+        <v>1</v>
       </c>
       <c r="F28" t="n">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="G28" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="29">
@@ -1414,23 +1259,22 @@
           <t>Morado</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="C29" t="n">
+        <v>1</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="E29" t="n">
+        <v>0</v>
       </c>
       <c r="F29" t="n">
-        <v>5</v>
+        <v>0</v>
+      </c>
+      <c r="G29" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -1444,23 +1288,22 @@
           <t>Morado</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="C30" t="n">
+        <v>1</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
           <t>G</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="E30" t="n">
+        <v>2</v>
       </c>
       <c r="F30" t="n">
-        <v>6</v>
+        <v>2</v>
+      </c>
+      <c r="G30" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="31">
@@ -1474,23 +1317,22 @@
           <t>Morado</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="C31" t="n">
+        <v>1</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
           <t>XL</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="E31" t="n">
+        <v>0</v>
       </c>
       <c r="F31" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="G31" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="32">
@@ -1504,25 +1346,22 @@
           <t>Negro</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="C32" t="n">
+        <v>1</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
           <t>XC</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="E32" t="n">
+        <v>1</v>
+      </c>
+      <c r="F32" t="n">
+        <v>0</v>
+      </c>
+      <c r="G32" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="33">
@@ -1536,25 +1375,22 @@
           <t>Negro</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="C33" t="n">
+        <v>1</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="E33" t="n">
+        <v>1</v>
+      </c>
+      <c r="F33" t="n">
+        <v>0</v>
+      </c>
+      <c r="G33" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="34">
@@ -1568,25 +1404,22 @@
           <t>Negro</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="C34" t="n">
+        <v>1</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="E34" t="n">
+        <v>2</v>
+      </c>
+      <c r="F34" t="n">
+        <v>2</v>
+      </c>
+      <c r="G34" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="35">
@@ -1600,25 +1433,22 @@
           <t>Negro</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="C35" t="n">
+        <v>1</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
           <t>G</t>
         </is>
       </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="E35" t="n">
+        <v>2</v>
+      </c>
+      <c r="F35" t="n">
+        <v>2</v>
+      </c>
+      <c r="G35" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="36">
@@ -1632,25 +1462,22 @@
           <t>Negro</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="C36" t="n">
+        <v>1</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
           <t>XL</t>
         </is>
       </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="E36" t="n">
+        <v>1</v>
+      </c>
+      <c r="F36" t="n">
+        <v>1</v>
+      </c>
+      <c r="G36" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="37">
@@ -1664,25 +1491,22 @@
           <t>Gris</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="C37" t="n">
+        <v>1</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
           <t>XC</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="E37" t="n">
+        <v>0</v>
+      </c>
+      <c r="F37" t="n">
+        <v>0</v>
+      </c>
+      <c r="G37" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="38">
@@ -1696,25 +1520,22 @@
           <t>Gris</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="C38" t="n">
+        <v>1</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="E38" t="n">
+        <v>1</v>
+      </c>
+      <c r="F38" t="n">
+        <v>1</v>
+      </c>
+      <c r="G38" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="39">
@@ -1728,23 +1549,22 @@
           <t>Gris</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="C39" t="n">
+        <v>1</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="E39" t="n">
+        <v>0</v>
       </c>
       <c r="F39" t="n">
-        <v>2</v>
+        <v>0</v>
+      </c>
+      <c r="G39" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="40">
@@ -1758,23 +1578,22 @@
           <t>Gris</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="C40" t="n">
+        <v>1</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
           <t>G</t>
         </is>
       </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="E40" t="n">
+        <v>2</v>
       </c>
       <c r="F40" t="n">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="G40" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="41">
@@ -1788,25 +1607,22 @@
           <t>Gris</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="C41" t="n">
+        <v>1</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
           <t>XL</t>
         </is>
       </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="E41" t="n">
+        <v>0</v>
+      </c>
+      <c r="F41" t="n">
+        <v>0</v>
+      </c>
+      <c r="G41" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="42">
@@ -1820,25 +1636,22 @@
           <t>Blanco</t>
         </is>
       </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="C42" t="n">
+        <v>2</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
           <t>XC</t>
         </is>
       </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="E42" t="n">
+        <v>1</v>
+      </c>
+      <c r="F42" t="n">
+        <v>0</v>
+      </c>
+      <c r="G42" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="43">
@@ -1852,25 +1665,22 @@
           <t>Blanco</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="C43" t="n">
+        <v>2</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="E43" t="n">
+        <v>2</v>
+      </c>
+      <c r="F43" t="n">
+        <v>1</v>
+      </c>
+      <c r="G43" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="44">
@@ -1884,25 +1694,22 @@
           <t>Blanco</t>
         </is>
       </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="C44" t="n">
+        <v>2</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="E44" t="n">
+        <v>1</v>
+      </c>
+      <c r="F44" t="n">
+        <v>0</v>
+      </c>
+      <c r="G44" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="45">
@@ -1916,25 +1723,22 @@
           <t>Blanco</t>
         </is>
       </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="C45" t="n">
+        <v>2</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
           <t>G</t>
         </is>
       </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="E45" t="n">
+        <v>1</v>
+      </c>
+      <c r="F45" t="n">
+        <v>1</v>
+      </c>
+      <c r="G45" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="46">
@@ -1948,25 +1752,22 @@
           <t>Blanco</t>
         </is>
       </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="C46" t="n">
+        <v>2</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
           <t>XL</t>
         </is>
       </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="E46" t="n">
+        <v>0</v>
+      </c>
+      <c r="F46" t="n">
+        <v>0</v>
+      </c>
+      <c r="G46" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="47">
@@ -1980,25 +1781,22 @@
           <t>Rosa</t>
         </is>
       </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="C47" t="n">
+        <v>2</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
           <t>XC</t>
         </is>
       </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="E47" t="n">
+        <v>1</v>
+      </c>
+      <c r="F47" t="n">
+        <v>1</v>
+      </c>
+      <c r="G47" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="48">
@@ -2012,23 +1810,22 @@
           <t>Rosa</t>
         </is>
       </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="C48" t="n">
+        <v>2</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="E48" t="n">
+        <v>0</v>
       </c>
       <c r="F48" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="G48" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -2042,22 +1839,21 @@
           <t>Rosa</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="C49" t="n">
+        <v>2</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="E49" t="n">
+        <v>2</v>
       </c>
       <c r="F49" t="n">
+        <v>1</v>
+      </c>
+      <c r="G49" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2072,25 +1868,22 @@
           <t>Rosa</t>
         </is>
       </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="C50" t="n">
+        <v>2</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
           <t>G</t>
         </is>
       </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="E50" t="n">
+        <v>0</v>
+      </c>
+      <c r="F50" t="n">
+        <v>0</v>
+      </c>
+      <c r="G50" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="51">
@@ -2104,25 +1897,22 @@
           <t>Rosa</t>
         </is>
       </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="C51" t="n">
+        <v>2</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
           <t>XL</t>
         </is>
       </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="E51" t="n">
+        <v>0</v>
+      </c>
+      <c r="F51" t="n">
+        <v>0</v>
+      </c>
+      <c r="G51" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="52">
@@ -2136,25 +1926,22 @@
           <t>Negro</t>
         </is>
       </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="C52" t="n">
+        <v>2</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
           <t>XC</t>
         </is>
       </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="E52" t="n">
+        <v>1</v>
+      </c>
+      <c r="F52" t="n">
+        <v>0</v>
+      </c>
+      <c r="G52" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="53">
@@ -2168,25 +1955,22 @@
           <t>Negro</t>
         </is>
       </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="C53" t="n">
+        <v>2</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="E53" t="n">
+        <v>5</v>
+      </c>
+      <c r="F53" t="n">
+        <v>1</v>
+      </c>
+      <c r="G53" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="54">
@@ -2200,25 +1984,22 @@
           <t>Negro</t>
         </is>
       </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="C54" t="n">
+        <v>2</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="E54" t="n">
+        <v>5</v>
+      </c>
+      <c r="F54" t="n">
+        <v>0</v>
+      </c>
+      <c r="G54" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="55">
@@ -2232,25 +2013,22 @@
           <t>Negro</t>
         </is>
       </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="C55" t="n">
+        <v>2</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
           <t>G</t>
         </is>
       </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="E55" t="n">
+        <v>5</v>
+      </c>
+      <c r="F55" t="n">
+        <v>3</v>
+      </c>
+      <c r="G55" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="56">
@@ -2264,25 +2042,22 @@
           <t>Negro</t>
         </is>
       </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="C56" t="n">
+        <v>2</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
           <t>XL</t>
         </is>
       </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="E56" t="n">
+        <v>0</v>
+      </c>
+      <c r="F56" t="n">
+        <v>0</v>
+      </c>
+      <c r="G56" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="57">
@@ -2296,25 +2071,22 @@
           <t>Navy</t>
         </is>
       </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="C57" t="n">
+        <v>2</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
           <t>XC</t>
         </is>
       </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="E57" t="n">
+        <v>0</v>
+      </c>
+      <c r="F57" t="n">
+        <v>0</v>
+      </c>
+      <c r="G57" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="58">
@@ -2328,25 +2100,22 @@
           <t>Navy</t>
         </is>
       </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="C58" t="n">
+        <v>2</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="E58" t="n">
+        <v>0</v>
+      </c>
+      <c r="F58" t="n">
+        <v>0</v>
+      </c>
+      <c r="G58" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="59">
@@ -2360,25 +2129,22 @@
           <t>Navy</t>
         </is>
       </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="C59" t="n">
+        <v>2</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="E59" t="n">
+        <v>3</v>
+      </c>
+      <c r="F59" t="n">
+        <v>1</v>
+      </c>
+      <c r="G59" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="60">
@@ -2392,25 +2158,22 @@
           <t>Navy</t>
         </is>
       </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="C60" t="n">
+        <v>2</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
           <t>G</t>
         </is>
       </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="E60" t="n">
+        <v>0</v>
+      </c>
+      <c r="F60" t="n">
+        <v>0</v>
+      </c>
+      <c r="G60" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="61">
@@ -2424,25 +2187,22 @@
           <t>Navy</t>
         </is>
       </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="C61" t="n">
+        <v>2</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
           <t>XL</t>
         </is>
       </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="E61" t="n">
+        <v>0</v>
+      </c>
+      <c r="F61" t="n">
+        <v>0</v>
+      </c>
+      <c r="G61" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="62">
@@ -2456,25 +2216,22 @@
           <t>Carbon</t>
         </is>
       </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="C62" t="n">
+        <v>2</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
           <t>XC</t>
         </is>
       </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="E62" t="n">
+        <v>1</v>
+      </c>
+      <c r="F62" t="n">
+        <v>0</v>
+      </c>
+      <c r="G62" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="63">
@@ -2488,25 +2245,22 @@
           <t>Carbon</t>
         </is>
       </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="C63" t="n">
+        <v>2</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="E63" t="n">
+        <v>1</v>
+      </c>
+      <c r="F63" t="n">
+        <v>0</v>
+      </c>
+      <c r="G63" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="64">
@@ -2520,25 +2274,22 @@
           <t>Carbon</t>
         </is>
       </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="C64" t="n">
+        <v>2</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="E64" t="n">
+        <v>5</v>
+      </c>
+      <c r="F64" t="n">
+        <v>1</v>
+      </c>
+      <c r="G64" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="65">
@@ -2552,25 +2303,22 @@
           <t>Carbon</t>
         </is>
       </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="C65" t="n">
+        <v>2</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
           <t>G</t>
         </is>
       </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="E65" t="n">
+        <v>0</v>
+      </c>
+      <c r="F65" t="n">
+        <v>0</v>
+      </c>
+      <c r="G65" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="66">
@@ -2584,23 +2332,22 @@
           <t>Carbon</t>
         </is>
       </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="C66" t="n">
+        <v>2</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
           <t>XL</t>
         </is>
       </c>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="E66" t="n">
+        <v>0</v>
       </c>
       <c r="F66" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="G66" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="67">
@@ -2614,25 +2361,22 @@
           <t>Aqua</t>
         </is>
       </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="C67" t="n">
+        <v>2</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
           <t>XC</t>
         </is>
       </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="E67" t="n">
+        <v>0</v>
+      </c>
+      <c r="F67" t="n">
+        <v>0</v>
+      </c>
+      <c r="G67" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="68">
@@ -2646,25 +2390,22 @@
           <t>Aqua</t>
         </is>
       </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="C68" t="n">
+        <v>2</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="E68" t="n">
+        <v>1</v>
+      </c>
+      <c r="F68" t="n">
+        <v>1</v>
+      </c>
+      <c r="G68" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="69">
@@ -2678,25 +2419,22 @@
           <t>Aqua</t>
         </is>
       </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="C69" t="n">
+        <v>2</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="E69" t="n">
+        <v>2</v>
+      </c>
+      <c r="F69" t="n">
+        <v>1</v>
+      </c>
+      <c r="G69" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="70">
@@ -2710,23 +2448,22 @@
           <t>Aqua</t>
         </is>
       </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="C70" t="n">
+        <v>2</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
           <t>G</t>
         </is>
       </c>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="E70" t="n">
+        <v>2</v>
       </c>
       <c r="F70" t="n">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="G70" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="71">
@@ -2740,25 +2477,22 @@
           <t>Aqua</t>
         </is>
       </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="C71" t="n">
+        <v>2</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
           <t>XL</t>
         </is>
       </c>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="E71" t="n">
+        <v>0</v>
+      </c>
+      <c r="F71" t="n">
+        <v>0</v>
+      </c>
+      <c r="G71" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="72">
@@ -2772,25 +2506,22 @@
           <t>Verde</t>
         </is>
       </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="C72" t="n">
+        <v>2</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
           <t>XC</t>
         </is>
       </c>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="E72" t="n">
+        <v>0</v>
+      </c>
+      <c r="F72" t="n">
+        <v>0</v>
+      </c>
+      <c r="G72" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="73">
@@ -2804,23 +2535,22 @@
           <t>Verde</t>
         </is>
       </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="C73" t="n">
+        <v>2</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="E73" t="n">
+        <v>0</v>
       </c>
       <c r="F73" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="G73" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="74">
@@ -2834,25 +2564,22 @@
           <t>Verde</t>
         </is>
       </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="C74" t="n">
+        <v>2</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="E74" t="n">
+        <v>1</v>
+      </c>
+      <c r="F74" t="n">
+        <v>0</v>
+      </c>
+      <c r="G74" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="75">
@@ -2866,25 +2593,22 @@
           <t>Verde</t>
         </is>
       </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="C75" t="n">
+        <v>2</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
           <t>G</t>
         </is>
       </c>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="E75" t="n">
+        <v>1</v>
+      </c>
+      <c r="F75" t="n">
+        <v>1</v>
+      </c>
+      <c r="G75" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="76">
@@ -2898,25 +2622,22 @@
           <t>Verde</t>
         </is>
       </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="C76" t="n">
+        <v>2</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
           <t>XL</t>
         </is>
       </c>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="E76" t="n">
+        <v>3</v>
+      </c>
+      <c r="F76" t="n">
+        <v>1</v>
+      </c>
+      <c r="G76" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="77">
@@ -2930,25 +2651,22 @@
           <t>Verde</t>
         </is>
       </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="C77" t="n">
+        <v>2</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
           <t>XC</t>
         </is>
       </c>
-      <c r="E77" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="E77" t="n">
+        <v>0</v>
+      </c>
+      <c r="F77" t="n">
+        <v>0</v>
+      </c>
+      <c r="G77" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="78">
@@ -2962,25 +2680,22 @@
           <t>Verde</t>
         </is>
       </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="C78" t="n">
+        <v>2</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="E78" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="E78" t="n">
+        <v>2</v>
+      </c>
+      <c r="F78" t="n">
+        <v>0</v>
+      </c>
+      <c r="G78" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="79">
@@ -2994,25 +2709,22 @@
           <t>Verde</t>
         </is>
       </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="C79" t="n">
+        <v>2</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="E79" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="E79" t="n">
+        <v>2</v>
+      </c>
+      <c r="F79" t="n">
+        <v>0</v>
+      </c>
+      <c r="G79" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="80">
@@ -3026,25 +2738,22 @@
           <t>Verde</t>
         </is>
       </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="C80" t="n">
+        <v>2</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
           <t>G</t>
         </is>
       </c>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="E80" t="n">
+        <v>1</v>
+      </c>
+      <c r="F80" t="n">
+        <v>0</v>
+      </c>
+      <c r="G80" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="81">
@@ -3058,25 +2767,22 @@
           <t>Verde</t>
         </is>
       </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="C81" t="n">
+        <v>2</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
           <t>XL</t>
         </is>
       </c>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="E81" t="n">
+        <v>0</v>
+      </c>
+      <c r="F81" t="n">
+        <v>0</v>
+      </c>
+      <c r="G81" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="82">
@@ -3090,25 +2796,22 @@
           <t>Morado</t>
         </is>
       </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="C82" t="n">
+        <v>2</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
           <t>XC</t>
         </is>
       </c>
-      <c r="E82" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="E82" t="n">
+        <v>0</v>
+      </c>
+      <c r="F82" t="n">
+        <v>0</v>
+      </c>
+      <c r="G82" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="83">
@@ -3122,25 +2825,22 @@
           <t>Morado</t>
         </is>
       </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="C83" t="n">
+        <v>2</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="E83" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="E83" t="n">
+        <v>0</v>
+      </c>
+      <c r="F83" t="n">
+        <v>0</v>
+      </c>
+      <c r="G83" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="84">
@@ -3154,25 +2854,22 @@
           <t>Morado</t>
         </is>
       </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="C84" t="n">
+        <v>2</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="E84" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="F84" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="E84" t="n">
+        <v>2</v>
+      </c>
+      <c r="F84" t="n">
+        <v>1</v>
+      </c>
+      <c r="G84" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="85">
@@ -3186,23 +2883,22 @@
           <t>Morado</t>
         </is>
       </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="C85" t="n">
+        <v>2</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
           <t>G</t>
         </is>
       </c>
-      <c r="E85" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="E85" t="n">
+        <v>1</v>
       </c>
       <c r="F85" t="n">
-        <v>3</v>
+        <v>1</v>
+      </c>
+      <c r="G85" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="86">
@@ -3216,25 +2912,22 @@
           <t>Morado</t>
         </is>
       </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="C86" t="n">
+        <v>2</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
           <t>XL</t>
         </is>
       </c>
-      <c r="E86" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F86" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="E86" t="n">
+        <v>0</v>
+      </c>
+      <c r="F86" t="n">
+        <v>0</v>
+      </c>
+      <c r="G86" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="87">
@@ -3248,25 +2941,22 @@
           <t>Negro</t>
         </is>
       </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="C87" t="n">
+        <v>2</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
           <t>XC</t>
         </is>
       </c>
-      <c r="E87" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="E87" t="n">
+        <v>1</v>
+      </c>
+      <c r="F87" t="n">
+        <v>0</v>
+      </c>
+      <c r="G87" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="88">
@@ -3280,25 +2970,22 @@
           <t>Negro</t>
         </is>
       </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="C88" t="n">
+        <v>2</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="E88" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="E88" t="n">
+        <v>2</v>
+      </c>
+      <c r="F88" t="n">
+        <v>0</v>
+      </c>
+      <c r="G88" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="89">
@@ -3312,25 +2999,22 @@
           <t>Negro</t>
         </is>
       </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="C89" t="n">
+        <v>2</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="E89" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="F89" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="E89" t="n">
+        <v>3</v>
+      </c>
+      <c r="F89" t="n">
+        <v>2</v>
+      </c>
+      <c r="G89" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="90">
@@ -3344,25 +3028,22 @@
           <t>Negro</t>
         </is>
       </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="C90" t="n">
+        <v>2</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
           <t>G</t>
         </is>
       </c>
-      <c r="E90" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F90" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="E90" t="n">
+        <v>1</v>
+      </c>
+      <c r="F90" t="n">
+        <v>1</v>
+      </c>
+      <c r="G90" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="91">
@@ -3376,25 +3057,22 @@
           <t>Negro</t>
         </is>
       </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="C91" t="n">
+        <v>2</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
           <t>XL</t>
         </is>
       </c>
-      <c r="E91" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F91" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="E91" t="n">
+        <v>0</v>
+      </c>
+      <c r="F91" t="n">
+        <v>0</v>
+      </c>
+      <c r="G91" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="92">
@@ -3408,25 +3086,22 @@
           <t>Gris</t>
         </is>
       </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="C92" t="n">
+        <v>2</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
           <t>XC</t>
         </is>
       </c>
-      <c r="E92" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="E92" t="n">
+        <v>0</v>
+      </c>
+      <c r="F92" t="n">
+        <v>0</v>
+      </c>
+      <c r="G92" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="93">
@@ -3440,25 +3115,22 @@
           <t>Gris</t>
         </is>
       </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="C93" t="n">
+        <v>2</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="E93" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F93" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="E93" t="n">
+        <v>1</v>
+      </c>
+      <c r="F93" t="n">
+        <v>0</v>
+      </c>
+      <c r="G93" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="94">
@@ -3472,25 +3144,22 @@
           <t>Gris</t>
         </is>
       </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="C94" t="n">
+        <v>2</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="E94" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="E94" t="n">
+        <v>1</v>
+      </c>
+      <c r="F94" t="n">
+        <v>0</v>
+      </c>
+      <c r="G94" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="95">
@@ -3504,25 +3173,22 @@
           <t>Gris</t>
         </is>
       </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="C95" t="n">
+        <v>2</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
           <t>G</t>
         </is>
       </c>
-      <c r="E95" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F95" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="E95" t="n">
+        <v>1</v>
+      </c>
+      <c r="F95" t="n">
+        <v>0</v>
+      </c>
+      <c r="G95" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="96">
@@ -3536,25 +3202,22 @@
           <t>Gris</t>
         </is>
       </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="C96" t="n">
+        <v>2</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
           <t>XL</t>
         </is>
       </c>
-      <c r="E96" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F96" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="E96" t="n">
+        <v>0</v>
+      </c>
+      <c r="F96" t="n">
+        <v>0</v>
+      </c>
+      <c r="G96" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="97">
@@ -3568,25 +3231,22 @@
           <t>Negro</t>
         </is>
       </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="C97" t="n">
+        <v>2</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
           <t>XC</t>
         </is>
       </c>
-      <c r="E97" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F97" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="E97" t="n">
+        <v>0</v>
+      </c>
+      <c r="F97" t="n">
+        <v>0</v>
+      </c>
+      <c r="G97" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="98">
@@ -3600,25 +3260,22 @@
           <t>Negro</t>
         </is>
       </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="C98" t="n">
+        <v>2</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="E98" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F98" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="E98" t="n">
+        <v>1</v>
+      </c>
+      <c r="F98" t="n">
+        <v>0</v>
+      </c>
+      <c r="G98" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="99">
@@ -3632,25 +3289,22 @@
           <t>Negro</t>
         </is>
       </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="C99" t="n">
+        <v>2</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="E99" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="F99" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="E99" t="n">
+        <v>3</v>
+      </c>
+      <c r="F99" t="n">
+        <v>2</v>
+      </c>
+      <c r="G99" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="100">
@@ -3664,25 +3318,22 @@
           <t>Negro</t>
         </is>
       </c>
-      <c r="C100" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="C100" t="n">
+        <v>2</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
           <t>G</t>
         </is>
       </c>
-      <c r="E100" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F100" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="E100" t="n">
+        <v>1</v>
+      </c>
+      <c r="F100" t="n">
+        <v>0</v>
+      </c>
+      <c r="G100" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="101">
@@ -3696,25 +3347,22 @@
           <t>Negro</t>
         </is>
       </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="C101" t="n">
+        <v>2</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
           <t>XL</t>
         </is>
       </c>
-      <c r="E101" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F101" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="E101" t="n">
+        <v>0</v>
+      </c>
+      <c r="F101" t="n">
+        <v>0</v>
+      </c>
+      <c r="G101" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="102">
@@ -3728,25 +3376,22 @@
           <t>Verde</t>
         </is>
       </c>
-      <c r="C102" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="C102" t="n">
+        <v>3</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
           <t>XC</t>
         </is>
       </c>
-      <c r="E102" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F102" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="E102" t="n">
+        <v>1</v>
+      </c>
+      <c r="F102" t="n">
+        <v>0</v>
+      </c>
+      <c r="G102" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="103">
@@ -3760,25 +3405,22 @@
           <t>Verde</t>
         </is>
       </c>
-      <c r="C103" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="C103" t="n">
+        <v>3</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="E103" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="F103" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="E103" t="n">
+        <v>2</v>
+      </c>
+      <c r="F103" t="n">
+        <v>1</v>
+      </c>
+      <c r="G103" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="104">
@@ -3792,25 +3434,22 @@
           <t>Verde</t>
         </is>
       </c>
-      <c r="C104" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="C104" t="n">
+        <v>3</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="E104" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F104" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="E104" t="n">
+        <v>0</v>
+      </c>
+      <c r="F104" t="n">
+        <v>0</v>
+      </c>
+      <c r="G104" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="105">
@@ -3824,25 +3463,22 @@
           <t>Verde</t>
         </is>
       </c>
-      <c r="C105" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="C105" t="n">
+        <v>3</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
           <t>G</t>
         </is>
       </c>
-      <c r="E105" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F105" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="E105" t="n">
+        <v>0</v>
+      </c>
+      <c r="F105" t="n">
+        <v>0</v>
+      </c>
+      <c r="G105" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="106">
@@ -3856,25 +3492,22 @@
           <t>Verde</t>
         </is>
       </c>
-      <c r="C106" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="C106" t="n">
+        <v>3</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
           <t>XL</t>
         </is>
       </c>
-      <c r="E106" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F106" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="E106" t="n">
+        <v>0</v>
+      </c>
+      <c r="F106" t="n">
+        <v>0</v>
+      </c>
+      <c r="G106" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="107">
@@ -3888,25 +3521,22 @@
           <t>Morado</t>
         </is>
       </c>
-      <c r="C107" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="C107" t="n">
+        <v>3</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
           <t>XC</t>
         </is>
       </c>
-      <c r="E107" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F107" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="E107" t="n">
+        <v>1</v>
+      </c>
+      <c r="F107" t="n">
+        <v>1</v>
+      </c>
+      <c r="G107" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="108">
@@ -3920,25 +3550,22 @@
           <t>Morado</t>
         </is>
       </c>
-      <c r="C108" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="C108" t="n">
+        <v>3</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="E108" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="F108" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="E108" t="n">
+        <v>2</v>
+      </c>
+      <c r="F108" t="n">
+        <v>2</v>
+      </c>
+      <c r="G108" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="109">
@@ -3952,25 +3579,22 @@
           <t>Morado</t>
         </is>
       </c>
-      <c r="C109" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="C109" t="n">
+        <v>3</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="E109" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F109" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="E109" t="n">
+        <v>0</v>
+      </c>
+      <c r="F109" t="n">
+        <v>0</v>
+      </c>
+      <c r="G109" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="110">
@@ -3984,25 +3608,22 @@
           <t>Morado</t>
         </is>
       </c>
-      <c r="C110" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="C110" t="n">
+        <v>3</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
           <t>G</t>
         </is>
       </c>
-      <c r="E110" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F110" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="E110" t="n">
+        <v>0</v>
+      </c>
+      <c r="F110" t="n">
+        <v>0</v>
+      </c>
+      <c r="G110" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="111">
@@ -4016,25 +3637,22 @@
           <t>Morado</t>
         </is>
       </c>
-      <c r="C111" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="C111" t="n">
+        <v>3</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
           <t>XL</t>
         </is>
       </c>
-      <c r="E111" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F111" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="E111" t="n">
+        <v>0</v>
+      </c>
+      <c r="F111" t="n">
+        <v>0</v>
+      </c>
+      <c r="G111" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="112">
@@ -4048,25 +3666,22 @@
           <t>Negro</t>
         </is>
       </c>
-      <c r="C112" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="C112" t="n">
+        <v>3</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
           <t>XC</t>
         </is>
       </c>
-      <c r="E112" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F112" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="E112" t="n">
+        <v>1</v>
+      </c>
+      <c r="F112" t="n">
+        <v>0</v>
+      </c>
+      <c r="G112" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="113">
@@ -4080,25 +3695,22 @@
           <t>Negro</t>
         </is>
       </c>
-      <c r="C113" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="C113" t="n">
+        <v>3</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="E113" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="F113" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="E113" t="n">
+        <v>3</v>
+      </c>
+      <c r="F113" t="n">
+        <v>2</v>
+      </c>
+      <c r="G113" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="114">
@@ -4112,25 +3724,22 @@
           <t>Negro</t>
         </is>
       </c>
-      <c r="C114" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="C114" t="n">
+        <v>3</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="E114" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F114" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="E114" t="n">
+        <v>2</v>
+      </c>
+      <c r="F114" t="n">
+        <v>0</v>
+      </c>
+      <c r="G114" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="115">
@@ -4144,25 +3753,22 @@
           <t>Negro</t>
         </is>
       </c>
-      <c r="C115" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="C115" t="n">
+        <v>3</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
           <t>G</t>
         </is>
       </c>
-      <c r="E115" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F115" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="E115" t="n">
+        <v>0</v>
+      </c>
+      <c r="F115" t="n">
+        <v>0</v>
+      </c>
+      <c r="G115" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="116">
@@ -4176,25 +3782,22 @@
           <t>Negro</t>
         </is>
       </c>
-      <c r="C116" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="C116" t="n">
+        <v>3</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
           <t>XL</t>
         </is>
       </c>
-      <c r="E116" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F116" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="E116" t="n">
+        <v>0</v>
+      </c>
+      <c r="F116" t="n">
+        <v>0</v>
+      </c>
+      <c r="G116" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="117">
@@ -4208,25 +3811,22 @@
           <t>Gris</t>
         </is>
       </c>
-      <c r="C117" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="C117" t="n">
+        <v>3</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
           <t>XS</t>
         </is>
       </c>
-      <c r="E117" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F117" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="E117" t="n">
+        <v>1</v>
+      </c>
+      <c r="F117" t="n">
+        <v>1</v>
+      </c>
+      <c r="G117" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="118">
@@ -4240,23 +3840,22 @@
           <t>Gris</t>
         </is>
       </c>
-      <c r="C118" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="C118" t="n">
+        <v>3</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="E118" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="E118" t="n">
+        <v>1</v>
       </c>
       <c r="F118" t="n">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="G118" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="119">
@@ -4270,23 +3869,22 @@
           <t>Gris</t>
         </is>
       </c>
-      <c r="C119" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="C119" t="n">
+        <v>3</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="E119" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="E119" t="n">
+        <v>1</v>
       </c>
       <c r="F119" t="n">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="G119" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="120">
@@ -4300,23 +3898,22 @@
           <t>Gris</t>
         </is>
       </c>
-      <c r="C120" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="C120" t="n">
+        <v>3</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
           <t>G</t>
         </is>
       </c>
-      <c r="E120" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="E120" t="n">
+        <v>1</v>
       </c>
       <c r="F120" t="n">
         <v>1</v>
+      </c>
+      <c r="G120" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="121">
@@ -4330,25 +3927,22 @@
           <t>Gris</t>
         </is>
       </c>
-      <c r="C121" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="C121" t="n">
+        <v>3</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
           <t>XL</t>
         </is>
       </c>
-      <c r="E121" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F121" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="E121" t="n">
+        <v>0</v>
+      </c>
+      <c r="F121" t="n">
+        <v>0</v>
+      </c>
+      <c r="G121" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="122">
@@ -4362,25 +3956,22 @@
           <t>Negro</t>
         </is>
       </c>
-      <c r="C122" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="C122" t="n">
+        <v>3</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
           <t>XC</t>
         </is>
       </c>
-      <c r="E122" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F122" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="E122" t="n">
+        <v>0</v>
+      </c>
+      <c r="F122" t="n">
+        <v>0</v>
+      </c>
+      <c r="G122" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="123">
@@ -4394,25 +3985,22 @@
           <t>Negro</t>
         </is>
       </c>
-      <c r="C123" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="C123" t="n">
+        <v>3</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="E123" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="F123" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="E123" t="n">
+        <v>2</v>
+      </c>
+      <c r="F123" t="n">
+        <v>2</v>
+      </c>
+      <c r="G123" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="124">
@@ -4426,25 +4014,22 @@
           <t>Negro</t>
         </is>
       </c>
-      <c r="C124" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="C124" t="n">
+        <v>3</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="E124" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="F124" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="E124" t="n">
+        <v>2</v>
+      </c>
+      <c r="F124" t="n">
+        <v>2</v>
+      </c>
+      <c r="G124" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="125">
@@ -4458,25 +4043,22 @@
           <t>Negro</t>
         </is>
       </c>
-      <c r="C125" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="C125" t="n">
+        <v>3</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
           <t>G</t>
         </is>
       </c>
-      <c r="E125" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F125" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="E125" t="n">
+        <v>0</v>
+      </c>
+      <c r="F125" t="n">
+        <v>0</v>
+      </c>
+      <c r="G125" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="126">
@@ -4490,25 +4072,22 @@
           <t>Negro</t>
         </is>
       </c>
-      <c r="C126" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="C126" t="n">
+        <v>3</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
           <t>XL</t>
         </is>
       </c>
-      <c r="E126" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F126" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="E126" t="n">
+        <v>0</v>
+      </c>
+      <c r="F126" t="n">
+        <v>0</v>
+      </c>
+      <c r="G126" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="127">
@@ -4522,25 +4101,22 @@
           <t>Blanco</t>
         </is>
       </c>
-      <c r="C127" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="C127" t="n">
+        <v>4</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
           <t>XC</t>
         </is>
       </c>
-      <c r="E127" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F127" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="E127" t="n">
+        <v>2</v>
+      </c>
+      <c r="F127" t="n">
+        <v>0</v>
+      </c>
+      <c r="G127" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="128">
@@ -4554,23 +4130,22 @@
           <t>Blanco</t>
         </is>
       </c>
-      <c r="C128" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="C128" t="n">
+        <v>4</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="E128" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="E128" t="n">
+        <v>3</v>
       </c>
       <c r="F128" t="n">
-        <v>3</v>
+        <v>2</v>
+      </c>
+      <c r="G128" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="129">
@@ -4584,25 +4159,22 @@
           <t>Blanco</t>
         </is>
       </c>
-      <c r="C129" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="C129" t="n">
+        <v>4</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="E129" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="F129" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="E129" t="n">
+        <v>4</v>
+      </c>
+      <c r="F129" t="n">
+        <v>1</v>
+      </c>
+      <c r="G129" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="130">
@@ -4616,25 +4188,22 @@
           <t>Blanco</t>
         </is>
       </c>
-      <c r="C130" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="C130" t="n">
+        <v>4</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
           <t>G</t>
         </is>
       </c>
-      <c r="E130" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="F130" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="E130" t="n">
+        <v>1</v>
+      </c>
+      <c r="F130" t="n">
+        <v>0</v>
+      </c>
+      <c r="G130" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="131">
@@ -4648,25 +4217,22 @@
           <t>Blanco</t>
         </is>
       </c>
-      <c r="C131" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="C131" t="n">
+        <v>4</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
           <t>XL</t>
         </is>
       </c>
-      <c r="E131" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F131" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="E131" t="n">
+        <v>0</v>
+      </c>
+      <c r="F131" t="n">
+        <v>0</v>
+      </c>
+      <c r="G131" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="132">
@@ -4680,25 +4246,22 @@
           <t>Negro</t>
         </is>
       </c>
-      <c r="C132" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="C132" t="n">
+        <v>4</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
           <t>XC</t>
         </is>
       </c>
-      <c r="E132" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F132" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="E132" t="n">
+        <v>1</v>
+      </c>
+      <c r="F132" t="n">
+        <v>1</v>
+      </c>
+      <c r="G132" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="133">
@@ -4712,25 +4275,22 @@
           <t>Negro</t>
         </is>
       </c>
-      <c r="C133" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="C133" t="n">
+        <v>4</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="E133" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F133" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="E133" t="n">
+        <v>2</v>
+      </c>
+      <c r="F133" t="n">
+        <v>0</v>
+      </c>
+      <c r="G133" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="134">
@@ -4744,23 +4304,22 @@
           <t>Negro</t>
         </is>
       </c>
-      <c r="C134" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="C134" t="n">
+        <v>4</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="E134" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="E134" t="n">
+        <v>7</v>
       </c>
       <c r="F134" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="G134" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="135">
@@ -4774,25 +4333,22 @@
           <t>Negro</t>
         </is>
       </c>
-      <c r="C135" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="C135" t="n">
+        <v>4</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
           <t>G</t>
         </is>
       </c>
-      <c r="E135" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="F135" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="E135" t="n">
+        <v>3</v>
+      </c>
+      <c r="F135" t="n">
+        <v>1</v>
+      </c>
+      <c r="G135" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="136">
@@ -4806,25 +4362,22 @@
           <t>Negro</t>
         </is>
       </c>
-      <c r="C136" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="C136" t="n">
+        <v>4</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
           <t>XL</t>
         </is>
       </c>
-      <c r="E136" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F136" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="E136" t="n">
+        <v>0</v>
+      </c>
+      <c r="F136" t="n">
+        <v>0</v>
+      </c>
+      <c r="G136" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="137">
@@ -4838,25 +4391,22 @@
           <t>Carbon</t>
         </is>
       </c>
-      <c r="C137" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="C137" t="n">
+        <v>4</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
           <t>XC</t>
         </is>
       </c>
-      <c r="E137" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F137" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="E137" t="n">
+        <v>0</v>
+      </c>
+      <c r="F137" t="n">
+        <v>0</v>
+      </c>
+      <c r="G137" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="138">
@@ -4870,25 +4420,22 @@
           <t>Carbon</t>
         </is>
       </c>
-      <c r="C138" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="C138" t="n">
+        <v>4</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="E138" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="F138" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="E138" t="n">
+        <v>3</v>
+      </c>
+      <c r="F138" t="n">
+        <v>0</v>
+      </c>
+      <c r="G138" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="139">
@@ -4902,25 +4449,22 @@
           <t>Carbon</t>
         </is>
       </c>
-      <c r="C139" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="C139" t="n">
+        <v>4</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="E139" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="F139" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="E139" t="n">
+        <v>3</v>
+      </c>
+      <c r="F139" t="n">
+        <v>0</v>
+      </c>
+      <c r="G139" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="140">
@@ -4934,25 +4478,22 @@
           <t>Carbon</t>
         </is>
       </c>
-      <c r="C140" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="C140" t="n">
+        <v>4</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
           <t>G</t>
         </is>
       </c>
-      <c r="E140" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="F140" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="E140" t="n">
+        <v>3</v>
+      </c>
+      <c r="F140" t="n">
+        <v>0</v>
+      </c>
+      <c r="G140" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="141">
@@ -4966,25 +4507,22 @@
           <t>Carbon</t>
         </is>
       </c>
-      <c r="C141" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="C141" t="n">
+        <v>4</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
           <t>XL</t>
         </is>
       </c>
-      <c r="E141" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F141" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="E141" t="n">
+        <v>0</v>
+      </c>
+      <c r="F141" t="n">
+        <v>0</v>
+      </c>
+      <c r="G141" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="142">
@@ -4998,25 +4536,22 @@
           <t>Navy</t>
         </is>
       </c>
-      <c r="C142" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="C142" t="n">
+        <v>4</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
           <t>XC</t>
         </is>
       </c>
-      <c r="E142" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F142" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="E142" t="n">
+        <v>0</v>
+      </c>
+      <c r="F142" t="n">
+        <v>0</v>
+      </c>
+      <c r="G142" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="143">
@@ -5030,25 +4565,22 @@
           <t>Navy</t>
         </is>
       </c>
-      <c r="C143" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="C143" t="n">
+        <v>4</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="E143" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="F143" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="E143" t="n">
+        <v>3</v>
+      </c>
+      <c r="F143" t="n">
+        <v>0</v>
+      </c>
+      <c r="G143" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="144">
@@ -5062,25 +4594,22 @@
           <t>Navy</t>
         </is>
       </c>
-      <c r="C144" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="C144" t="n">
+        <v>4</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="E144" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="F144" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="E144" t="n">
+        <v>3</v>
+      </c>
+      <c r="F144" t="n">
+        <v>0</v>
+      </c>
+      <c r="G144" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="145">
@@ -5094,25 +4623,22 @@
           <t>Navy</t>
         </is>
       </c>
-      <c r="C145" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="C145" t="n">
+        <v>4</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
           <t>G</t>
         </is>
       </c>
-      <c r="E145" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F145" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="E145" t="n">
+        <v>0</v>
+      </c>
+      <c r="F145" t="n">
+        <v>0</v>
+      </c>
+      <c r="G145" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="146">
@@ -5126,25 +4652,22 @@
           <t>Navy</t>
         </is>
       </c>
-      <c r="C146" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="C146" t="n">
+        <v>4</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
           <t>XL</t>
         </is>
       </c>
-      <c r="E146" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F146" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="E146" t="n">
+        <v>0</v>
+      </c>
+      <c r="F146" t="n">
+        <v>0</v>
+      </c>
+      <c r="G146" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="147">
@@ -5158,25 +4681,22 @@
           <t>Verde</t>
         </is>
       </c>
-      <c r="C147" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="C147" t="n">
+        <v>4</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
           <t>XC</t>
         </is>
       </c>
-      <c r="E147" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F147" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="E147" t="n">
+        <v>0</v>
+      </c>
+      <c r="F147" t="n">
+        <v>0</v>
+      </c>
+      <c r="G147" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="148">
@@ -5190,25 +4710,22 @@
           <t>Verde</t>
         </is>
       </c>
-      <c r="C148" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="C148" t="n">
+        <v>4</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="E148" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="F148" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="E148" t="n">
+        <v>1</v>
+      </c>
+      <c r="F148" t="n">
+        <v>1</v>
+      </c>
+      <c r="G148" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="149">
@@ -5222,25 +4739,22 @@
           <t>Verde</t>
         </is>
       </c>
-      <c r="C149" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="C149" t="n">
+        <v>4</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="E149" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="F149" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="E149" t="n">
+        <v>1</v>
+      </c>
+      <c r="F149" t="n">
+        <v>0</v>
+      </c>
+      <c r="G149" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="150">
@@ -5254,25 +4768,22 @@
           <t>Verde</t>
         </is>
       </c>
-      <c r="C150" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="C150" t="n">
+        <v>4</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
           <t>G</t>
         </is>
       </c>
-      <c r="E150" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="F150" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="E150" t="n">
+        <v>1</v>
+      </c>
+      <c r="F150" t="n">
+        <v>0</v>
+      </c>
+      <c r="G150" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="151">
@@ -5286,25 +4797,22 @@
           <t>Verde</t>
         </is>
       </c>
-      <c r="C151" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="C151" t="n">
+        <v>4</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
           <t>XL</t>
         </is>
       </c>
-      <c r="E151" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F151" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="E151" t="n">
+        <v>0</v>
+      </c>
+      <c r="F151" t="n">
+        <v>0</v>
+      </c>
+      <c r="G151" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="152">
@@ -5318,25 +4826,22 @@
           <t>Navy</t>
         </is>
       </c>
-      <c r="C152" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="C152" t="n">
+        <v>4</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
           <t>XC</t>
         </is>
       </c>
-      <c r="E152" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F152" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="E152" t="n">
+        <v>0</v>
+      </c>
+      <c r="F152" t="n">
+        <v>0</v>
+      </c>
+      <c r="G152" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="153">
@@ -5350,25 +4855,22 @@
           <t>Navy</t>
         </is>
       </c>
-      <c r="C153" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="C153" t="n">
+        <v>4</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="E153" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="F153" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="E153" t="n">
+        <v>1</v>
+      </c>
+      <c r="F153" t="n">
+        <v>1</v>
+      </c>
+      <c r="G153" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="154">
@@ -5382,25 +4884,22 @@
           <t>Navy</t>
         </is>
       </c>
-      <c r="C154" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="C154" t="n">
+        <v>4</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="E154" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="F154" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="E154" t="n">
+        <v>1</v>
+      </c>
+      <c r="F154" t="n">
+        <v>0</v>
+      </c>
+      <c r="G154" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="155">
@@ -5414,25 +4913,22 @@
           <t>Navy</t>
         </is>
       </c>
-      <c r="C155" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="C155" t="n">
+        <v>4</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
           <t>G</t>
         </is>
       </c>
-      <c r="E155" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="F155" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="E155" t="n">
+        <v>1</v>
+      </c>
+      <c r="F155" t="n">
+        <v>0</v>
+      </c>
+      <c r="G155" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="156">
@@ -5446,25 +4942,22 @@
           <t>Navy</t>
         </is>
       </c>
-      <c r="C156" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="C156" t="n">
+        <v>4</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
           <t>XL</t>
         </is>
       </c>
-      <c r="E156" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F156" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="E156" t="n">
+        <v>0</v>
+      </c>
+      <c r="F156" t="n">
+        <v>0</v>
+      </c>
+      <c r="G156" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="157">
@@ -5478,25 +4971,22 @@
           <t>Negro</t>
         </is>
       </c>
-      <c r="C157" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="C157" t="n">
+        <v>4</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
           <t>XC</t>
         </is>
       </c>
-      <c r="E157" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F157" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="E157" t="n">
+        <v>0</v>
+      </c>
+      <c r="F157" t="n">
+        <v>0</v>
+      </c>
+      <c r="G157" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="158">
@@ -5510,25 +5000,22 @@
           <t>Negro</t>
         </is>
       </c>
-      <c r="C158" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="C158" t="n">
+        <v>4</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="E158" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="F158" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="E158" t="n">
+        <v>1</v>
+      </c>
+      <c r="F158" t="n">
+        <v>0</v>
+      </c>
+      <c r="G158" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="159">
@@ -5542,25 +5029,22 @@
           <t>Negro</t>
         </is>
       </c>
-      <c r="C159" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="C159" t="n">
+        <v>4</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="E159" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="F159" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="E159" t="n">
+        <v>1</v>
+      </c>
+      <c r="F159" t="n">
+        <v>0</v>
+      </c>
+      <c r="G159" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="160">
@@ -5574,25 +5058,22 @@
           <t>Negro</t>
         </is>
       </c>
-      <c r="C160" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="C160" t="n">
+        <v>4</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
           <t>G</t>
         </is>
       </c>
-      <c r="E160" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="F160" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="E160" t="n">
+        <v>1</v>
+      </c>
+      <c r="F160" t="n">
+        <v>0</v>
+      </c>
+      <c r="G160" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="161">
@@ -5606,29 +5087,25 @@
           <t>Negro</t>
         </is>
       </c>
-      <c r="C161" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="C161" t="n">
+        <v>4</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
           <t>XL</t>
         </is>
       </c>
-      <c r="E161" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F161" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="E161" t="n">
+        <v>0</v>
+      </c>
+      <c r="F161" t="n">
+        <v>0</v>
+      </c>
+      <c r="G161" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <legacyDrawing r:id="anysvml"/>
 </worksheet>
 </file>
--- a/inventario_agonia.xlsx
+++ b/inventario_agonia.xlsx
@@ -2,15 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection/>
-  <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
-  </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="171027" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -46,10 +42,19 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -62,9 +67,9 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="00000000"/>
@@ -211,6 +216,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -245,6 +251,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -279,20 +286,16 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:shade val="51000"/>
-                <a:satMod val="130000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="80000">
-              <a:schemeClr val="phClr">
-                <a:shade val="93000"/>
+                <a:tint val="100000"/>
+                <a:shade val="100000"/>
                 <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="94000"/>
-                <a:satMod val="135000"/>
+                <a:tint val="50000"/>
+                <a:shade val="100000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
@@ -414,7 +417,46 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
+  <a:objectDefaults>
+    <a:spDef>
+      <a:spPr/>
+      <a:bodyPr/>
+      <a:lstStyle/>
+      <a:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="3">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </a:style>
+    </a:spDef>
+    <a:lnDef>
+      <a:spPr/>
+      <a:bodyPr/>
+      <a:lstStyle/>
+      <a:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </a:style>
+    </a:lnDef>
+  </a:objectDefaults>
   <a:extraClrSchemeLst/>
 </a:theme>
 </file>
@@ -426,7 +468,10 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:G161"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelRow="0"/>
+  <cols>
+    <col width="13.57142857142857" customWidth="1" min="1" max="24"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
@@ -836,10 +881,10 @@
         <v>7</v>
       </c>
       <c r="F14" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -1097,10 +1142,10 @@
         <v>4</v>
       </c>
       <c r="F23" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -1155,10 +1200,10 @@
         <v>3</v>
       </c>
       <c r="F25" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -1358,10 +1403,10 @@
         <v>1</v>
       </c>
       <c r="F32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33">
@@ -3156,10 +3201,10 @@
         <v>1</v>
       </c>
       <c r="F94" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G94" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="95">
@@ -3185,10 +3230,10 @@
         <v>1</v>
       </c>
       <c r="F95" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G95" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="96">
@@ -3388,10 +3433,10 @@
         <v>1</v>
       </c>
       <c r="F102" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G102" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="103">
@@ -3816,7 +3861,7 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>XS</t>
+          <t>XC</t>
         </is>
       </c>
       <c r="E117" t="n">
@@ -4287,10 +4332,10 @@
         <v>2</v>
       </c>
       <c r="F133" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G133" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="134">
@@ -5106,6 +5151,7 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" scale="100" fitToHeight="1" fitToWidth="1" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>
 </file>
--- a/inventario_agonia.xlsx
+++ b/inventario_agonia.xlsx
@@ -562,10 +562,10 @@
         <v>2</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -591,10 +591,10 @@
         <v>2</v>
       </c>
       <c r="F4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -910,10 +910,10 @@
         <v>6</v>
       </c>
       <c r="F15" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G15" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -1142,10 +1142,10 @@
         <v>4</v>
       </c>
       <c r="F23" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -1432,10 +1432,10 @@
         <v>1</v>
       </c>
       <c r="F33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34">
@@ -1983,10 +1983,10 @@
         <v>1</v>
       </c>
       <c r="F52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="53">
@@ -2038,13 +2038,13 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F54" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G54" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="55">
@@ -2067,13 +2067,13 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F55" t="n">
         <v>3</v>
       </c>
       <c r="G55" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="56">
@@ -2186,10 +2186,10 @@
         <v>3</v>
       </c>
       <c r="F59" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G59" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="60">
@@ -2273,10 +2273,10 @@
         <v>1</v>
       </c>
       <c r="F62" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G62" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="63">
@@ -2911,10 +2911,10 @@
         <v>2</v>
       </c>
       <c r="F84" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G84" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="85">
@@ -2998,10 +2998,10 @@
         <v>1</v>
       </c>
       <c r="F87" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G87" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="88">
@@ -3027,10 +3027,10 @@
         <v>2</v>
       </c>
       <c r="F88" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G88" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="89">
@@ -3198,13 +3198,13 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F94" t="n">
         <v>1</v>
       </c>
       <c r="G94" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="95">
@@ -3317,10 +3317,10 @@
         <v>1</v>
       </c>
       <c r="F98" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G98" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="99">
@@ -3346,10 +3346,10 @@
         <v>3</v>
       </c>
       <c r="F99" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G99" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="100">
@@ -3462,10 +3462,10 @@
         <v>2</v>
       </c>
       <c r="F103" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G103" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="104">
@@ -4158,10 +4158,10 @@
         <v>2</v>
       </c>
       <c r="F127" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G127" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="128">
@@ -4187,10 +4187,10 @@
         <v>3</v>
       </c>
       <c r="F128" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G128" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="129">
